--- a/artfynd/A 13950-2026 artfynd.xlsx
+++ b/artfynd/A 13950-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89093070</v>
+        <v>89093067</v>
       </c>
       <c r="B2" t="n">
-        <v>57585</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482617.178852574</v>
+        <v>482557</v>
       </c>
       <c r="R2" t="n">
-        <v>6686184.225278436</v>
+        <v>6686151</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -808,6 +803,399 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>89093069</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lövsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>482591</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6686159</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-04-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-04-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Trafikverkets arbete med konfliktpunkter</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind, Barbara Kühn, Tor Hansson Frank, André Dabolins</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>89093070</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lövsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>482617</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6686184</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-04-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-04-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Trafikverkets arbete med konfliktpunkter</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind, Barbara Kühn, Tor Hansson Frank, André Dabolins</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>89093066</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lövsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>482571</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6686158</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-04-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-04-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Trafikverkets arbete med konfliktpunkter</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind, Barbara Kühn, Tor Hansson Frank, André Dabolins</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13950-2026 artfynd.xlsx
+++ b/artfynd/A 13950-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89093067</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -934,6 +944,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89093069</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1065,6 +1080,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89093070</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1196,8 +1216,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89093066</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>